--- a/stakeholder_analysis/Stakeholder_Register.xlsx
+++ b/stakeholder_analysis/Stakeholder_Register.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaibh\Downloads\DLOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaibh\Downloads\DLOS\stakeholder_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126AC6E6-CB73-4ACB-B754-748B1BDC4ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFC3475-6074-429A-BF75-C38D8CD0AB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6ADB6E8-4C51-479E-A63D-7386903B6E9F}"/>
   </bookViews>
@@ -337,12 +337,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -351,22 +366,22 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -719,494 +734,494 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="J3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="F9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="J9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="F10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="F12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" s="1" t="s">
+      <c r="J12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="3" t="s">
         <v>81</v>
       </c>
     </row>
